--- a/요구사항정의서_엑셀양식_v3_1_3.xlsx
+++ b/요구사항정의서_엑셀양식_v3_1_3.xlsx
@@ -796,7 +796,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>기획중</t>
+          <t>테스트중</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">

--- a/요구사항정의서_엑셀양식_v3_1_3.xlsx
+++ b/요구사항정의서_엑셀양식_v3_1_3.xlsx
@@ -885,7 +885,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>기획중</t>
+          <t>테스트중</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">

--- a/요구사항정의서_엑셀양식_v3_1_3.xlsx
+++ b/요구사항정의서_엑셀양식_v3_1_3.xlsx
@@ -973,7 +973,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>기획중</t>
+          <t>테스트중</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">

--- a/요구사항정의서_엑셀양식_v3_1_3.xlsx
+++ b/요구사항정의서_엑셀양식_v3_1_3.xlsx
@@ -1060,7 +1060,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>기획중</t>
+          <t>테스트중</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">

--- a/요구사항정의서_엑셀양식_v3_1_3.xlsx
+++ b/요구사항정의서_엑셀양식_v3_1_3.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>기획중</t>
+          <t>테스트중</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">

--- a/요구사항정의서_엑셀양식_v3_1_3.xlsx
+++ b/요구사항정의서_엑셀양식_v3_1_3.xlsx
@@ -1232,7 +1232,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>기획중</t>
+          <t>테스트중</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">

--- a/요구사항정의서_엑셀양식_v3_1_3.xlsx
+++ b/요구사항정의서_엑셀양식_v3_1_3.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>기획중</t>
+          <t>테스트중</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">

--- a/요구사항정의서_엑셀양식_v3_1_3.xlsx
+++ b/요구사항정의서_엑셀양식_v3_1_3.xlsx
@@ -1406,7 +1406,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>기획중</t>
+          <t>테스트중</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">

--- a/요구사항정의서_엑셀양식_v3_1_3.xlsx
+++ b/요구사항정의서_엑셀양식_v3_1_3.xlsx
@@ -1493,7 +1493,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>기획중</t>
+          <t>테스트중</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">

--- a/요구사항정의서_엑셀양식_v3_1_3.xlsx
+++ b/요구사항정의서_엑셀양식_v3_1_3.xlsx
@@ -1580,7 +1580,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>기획중</t>
+          <t>테스트중</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">

--- a/요구사항정의서_엑셀양식_v3_1_3.xlsx
+++ b/요구사항정의서_엑셀양식_v3_1_3.xlsx
@@ -1667,7 +1667,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>기획중</t>
+          <t>테스트중</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">

--- a/요구사항정의서_엑셀양식_v3_1_3.xlsx
+++ b/요구사항정의서_엑셀양식_v3_1_3.xlsx
@@ -1754,7 +1754,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>기획중</t>
+          <t>테스트중</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">

--- a/요구사항정의서_엑셀양식_v3_1_3.xlsx
+++ b/요구사항정의서_엑셀양식_v3_1_3.xlsx
@@ -1841,7 +1841,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>기획중</t>
+          <t>테스트중</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">

--- a/요구사항정의서_엑셀양식_v3_1_3.xlsx
+++ b/요구사항정의서_엑셀양식_v3_1_3.xlsx
@@ -1928,7 +1928,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>기획중</t>
+          <t>테스트중</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
